--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.80541809032418</v>
+        <v>13.13088043967768</v>
       </c>
       <c r="D2" t="n">
-        <v>36.45888094826828</v>
+        <v>5.924568154093595</v>
       </c>
       <c r="E2" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F2" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.54099254031115</v>
+        <v>10.48791128780056</v>
       </c>
       <c r="D3" t="n">
-        <v>21.09502310972899</v>
+        <v>3.427941255330961</v>
       </c>
       <c r="E3" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F3" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.47597082812725</v>
+        <v>12.58984525957068</v>
       </c>
       <c r="D4" t="n">
-        <v>33.18508701209024</v>
+        <v>5.392576639464663</v>
       </c>
       <c r="E4" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F4" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>73.25984223981324</v>
+        <v>11.90472436396965</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4256733697054</v>
+        <v>4.944171922577127</v>
       </c>
       <c r="E5" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F5" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.56458519880569</v>
+        <v>9.029245094805924</v>
       </c>
       <c r="D6" t="n">
-        <v>11.88486432400471</v>
+        <v>1.931290452650766</v>
       </c>
       <c r="E6" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F6" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.14614013876437</v>
+        <v>5.38624777254921</v>
       </c>
       <c r="D7" t="n">
-        <v>13.64734406395618</v>
+        <v>2.217693410392879</v>
       </c>
       <c r="E7" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F7" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.9534610174919</v>
+        <v>5.029937415342434</v>
       </c>
       <c r="D8" t="n">
-        <v>3.244025256865108</v>
+        <v>0.52715410424058</v>
       </c>
       <c r="E8" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F8" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.93359460930107</v>
+        <v>3.564209124011424</v>
       </c>
       <c r="D9" t="n">
-        <v>12.77781280188437</v>
+        <v>2.07639458030621</v>
       </c>
       <c r="E9" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F9" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.04426681278756</v>
+        <v>5.857193357077979</v>
       </c>
       <c r="D10" t="n">
-        <v>32.88764968176186</v>
+        <v>5.344243073286303</v>
       </c>
       <c r="E10" t="n">
-        <v>21.22393574019356</v>
+        <v>3.448889557781455</v>
       </c>
       <c r="F10" t="n">
-        <v>11.21902562743642</v>
+        <v>1.823091664458418</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
